--- a/AAII_Financials/Yearly/B_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/B_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
   <si>
     <t>B</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1450900</v>
+      </c>
+      <c r="E8" s="3">
         <v>1261900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1258800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1124400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1491100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1495900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1436500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1230800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1194000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1262000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1091600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>928800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>865100</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1008800</v>
+      </c>
+      <c r="E9" s="3">
         <v>840000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>803900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>721200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>944200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>963500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1883100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>788700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>782800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>829600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>738200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>655700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>615300</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>442100</v>
+      </c>
+      <c r="E10" s="3">
         <v>421900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>455000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>403200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>547000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>532400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-446600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>442000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>411200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>432400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>353400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>273100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>249700</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,22 +873,23 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E12" s="3">
         <v>15800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>22900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>16900</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,32 +960,35 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E14" s="3">
         <v>80500</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2500</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>5400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>200</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -986,9 +1005,12 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1361900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1204700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1108800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1001000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1254700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1264100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1230000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1036500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1025600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1082000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>968400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>821600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>763500</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>89000</v>
+      </c>
+      <c r="E18" s="3">
         <v>57100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>150000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>123400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>236400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>231800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>206500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>194300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>168400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>180000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>123200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>107100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>101600</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-9000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-7400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3800</v>
-      </c>
-      <c r="J20" s="3">
-        <v>200</v>
       </c>
       <c r="K20" s="3">
         <v>200</v>
       </c>
       <c r="L20" s="3">
+        <v>200</v>
+      </c>
+      <c r="M20" s="3">
         <v>-2100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>207300</v>
+      </c>
+      <c r="E21" s="3">
         <v>145000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>235100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>205100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>326500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>318600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>300400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>274700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>246900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>259300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>185700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>161900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>160200</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>58200</v>
+      </c>
+      <c r="E22" s="3">
         <v>14600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>16200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>15900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>20600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>16800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>14600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>11900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>10700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>11400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>13100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>12200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>10300</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>33300</v>
+      </c>
+      <c r="E23" s="3">
         <v>38200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>127800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>101500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>206800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>207500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>195700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>182600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>157900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>166500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>107600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>92300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>91000</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E24" s="3">
         <v>24700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>27900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>38100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>48500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>38700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>37100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>47000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>36600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>46000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>35300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>12400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>16000</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E26" s="3">
         <v>13500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>99900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>63400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>158400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>168800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>158600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>135600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>121400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>120500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>72300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>79800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>75000</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E27" s="3">
         <v>13500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>99900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>63400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>158400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>168800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>158600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>135600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>121400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>120500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>72300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>79800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>75000</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1541,33 +1601,36 @@
       <c r="G29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3">
         <v>-2600</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-99200</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-2200</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>198200</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>15400</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-10200</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E32" s="3">
         <v>4300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>9000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>7400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3800</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-200</v>
       </c>
       <c r="K32" s="3">
         <v>-200</v>
       </c>
       <c r="L32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M32" s="3">
         <v>2100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E33" s="3">
         <v>13500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>99900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>63400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>158400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>166200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>59400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>135600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>121400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>118400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>270500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>95200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>64700</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E35" s="3">
         <v>13500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>99900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>63400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>158400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>166200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>59400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>135600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>121400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>118400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>270500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>95200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>64700</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,50 +1986,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>89800</v>
+      </c>
+      <c r="E41" s="3">
         <v>76900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>102900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>79100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>93800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>100700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>145300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>66400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>83900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>46000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>70900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>86400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>62500</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1984,177 +2073,192 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>413600</v>
+      </c>
+      <c r="E43" s="3">
         <v>334300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>295800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>284500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>371400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>394100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>348900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>287100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>261800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>275900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>258700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>253200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>200500</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>365200</v>
+      </c>
+      <c r="E44" s="3">
         <v>283400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>239700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>238000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>232700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>266000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>242000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>227800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>208600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>212000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>211200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>226200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>216500</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E45" s="3">
         <v>37700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>41900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>40700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>66500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>45300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>32500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>27200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>57300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>54400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>36400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>71600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>50500</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>906700</v>
+      </c>
+      <c r="E46" s="3">
         <v>732300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>680200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>642300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>764400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>806100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>768700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>608500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>611600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>588400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>577200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>618500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>530000</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2194,93 +2298,102 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>449500</v>
+      </c>
+      <c r="E48" s="3">
         <v>347200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>370900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>398500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>388000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>370500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>359300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>334500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>308900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>299400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>302600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>233100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>210800</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1890100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1278000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1455600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1575700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1514100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1592100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1197300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1155700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1116300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1149600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1184000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>930100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>638200</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>61700</v>
+      </c>
+      <c r="E52" s="3">
         <v>56300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>70100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>59700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>71800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>40200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>40400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>38900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>25100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>36400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>59900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>53100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>61400</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3308000</v>
+      </c>
+      <c r="E54" s="3">
         <v>2413700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2576800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2676200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2738300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2809000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2365700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2137500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2061900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2073900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2123700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1868600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1440400</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>164300</v>
+      </c>
+      <c r="E57" s="3">
         <v>145100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>131100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>112400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>118500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>143400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>127500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>112000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>97000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>94800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>88700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>99000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>92500</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E58" s="3">
         <v>1400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>9800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>32900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>24200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>57100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>12900</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>221500</v>
+      </c>
+      <c r="E59" s="3">
         <v>158600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>175600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>178600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>214600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>206800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>181200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>157000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>131300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>161400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>154500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>149500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>92300</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>396600</v>
+      </c>
+      <c r="E60" s="3">
         <v>305100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>310400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>295400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>342900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>357900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>315800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>301900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>252600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>265100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>300300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>199900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>197700</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1280000</v>
+      </c>
+      <c r="E61" s="3">
         <v>569600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>599900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>699900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>825000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>936400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>525600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>468100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>485700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>495800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>490300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>642100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>333100</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>269200</v>
+      </c>
+      <c r="E62" s="3">
         <v>192700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>237700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>298300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>292900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>311700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>264000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>199200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>195900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>201200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>191600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>226500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>187100</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1945800</v>
+      </c>
+      <c r="E66" s="3">
         <v>1067400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1148100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1293500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1467800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1605900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1105400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>969200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>934100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>962100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>982300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1068500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>718000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1551200</v>
+      </c>
+      <c r="E72" s="3">
         <v>1567900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1587000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1519800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1489200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1363800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1206700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1177200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1069200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>974500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>881200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>633400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>560200</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1362300</v>
+      </c>
+      <c r="E76" s="3">
         <v>1346300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1428800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1382700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1270500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1203100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1260300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1168400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1127800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1111800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1141400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>800100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>722400</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E81" s="3">
         <v>13500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>99900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>63400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>158400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>166200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>59400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>135600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>121400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>118400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>270500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>95200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>64700</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>115800</v>
+      </c>
+      <c r="E83" s="3">
         <v>92200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>91100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>87700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>99100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>94200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>90200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>80200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>78200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>81400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>65100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>57400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>58900</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>112400</v>
+      </c>
+      <c r="E89" s="3">
         <v>75600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>167800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>215500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>248300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>237200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>203900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>217600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>217500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>186900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>10100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>136400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>121000</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-55700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-35100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-34100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-40700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-53300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-57300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-58700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-47600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-46000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-57400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-57300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-37800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-37100</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-767500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-36000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-29800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-62200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-493200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-68000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-179500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-115500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-124200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>157400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-332800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-30600</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,8 +4220,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4003,35 +4236,38 @@
         <v>-32400</v>
       </c>
       <c r="G96" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="H96" s="3">
         <v>-32500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-32200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-29600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-27400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-26200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-24500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-22400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-21700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-18600</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>666600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-64800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-114700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-219700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-192000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>215600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-63800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-53300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-59200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-83500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-182800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>219300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-40200</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>6100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>6700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1200</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-30800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>20400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-44600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>78800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-17500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>37900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-24800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-15500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>23900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>49100</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/B_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/B_YR_FIN.xlsx
@@ -970,7 +970,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>12100</v>
+        <v>36000</v>
       </c>
       <c r="E14" s="3">
         <v>80500</v>
@@ -1076,7 +1076,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1361900</v>
+        <v>1371500</v>
       </c>
       <c r="E17" s="3">
         <v>1204700</v>
@@ -1121,7 +1121,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>89000</v>
+        <v>79400</v>
       </c>
       <c r="E18" s="3">
         <v>57100</v>
@@ -1230,7 +1230,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>207300</v>
+        <v>197600</v>
       </c>
       <c r="E21" s="3">
         <v>145000</v>
@@ -1275,7 +1275,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>58200</v>
+        <v>48600</v>
       </c>
       <c r="E22" s="3">
         <v>14600</v>

--- a/AAII_Financials/Yearly/B_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/B_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>B</t>
   </si>
@@ -771,10 +771,10 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1008800</v>
+        <v>995400</v>
       </c>
       <c r="E9" s="3">
-        <v>840000</v>
+        <v>836800</v>
       </c>
       <c r="F9" s="3">
         <v>803900</v>
@@ -789,7 +789,7 @@
         <v>963500</v>
       </c>
       <c r="J9" s="3">
-        <v>1883100</v>
+        <v>936300</v>
       </c>
       <c r="K9" s="3">
         <v>788700</v>
@@ -816,10 +816,10 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>442100</v>
+        <v>455500</v>
       </c>
       <c r="E10" s="3">
-        <v>421900</v>
+        <v>425100</v>
       </c>
       <c r="F10" s="3">
         <v>455000</v>
@@ -834,7 +834,7 @@
         <v>532400</v>
       </c>
       <c r="J10" s="3">
-        <v>-446600</v>
+        <v>500200</v>
       </c>
       <c r="K10" s="3">
         <v>442000</v>
@@ -891,14 +891,14 @@
       <c r="G12" s="3">
         <v>16900</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
+      <c r="H12" s="3">
+        <v>15700</v>
+      </c>
+      <c r="I12" s="3">
+        <v>16200</v>
+      </c>
+      <c r="J12" s="3">
+        <v>14800</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -970,19 +970,19 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>36000</v>
+        <v>71900</v>
       </c>
       <c r="E14" s="3">
-        <v>80500</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
+        <v>89900</v>
+      </c>
+      <c r="F14" s="3">
+        <v>2900</v>
       </c>
       <c r="G14" s="3">
-        <v>2500</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+        <v>19200</v>
+      </c>
+      <c r="H14" s="3">
+        <v>5900</v>
       </c>
       <c r="I14" s="3">
         <v>5400</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>112000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>89000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>91100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>87700</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>99100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>94200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>90200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1371500</v>
+        <v>1281000</v>
       </c>
       <c r="E17" s="3">
-        <v>1204700</v>
+        <v>1114900</v>
       </c>
       <c r="F17" s="3">
-        <v>1108800</v>
+        <v>1108300</v>
       </c>
       <c r="G17" s="3">
-        <v>1001000</v>
+        <v>983300</v>
       </c>
       <c r="H17" s="3">
-        <v>1254700</v>
+        <v>1248600</v>
       </c>
       <c r="I17" s="3">
-        <v>1264100</v>
+        <v>1260300</v>
       </c>
       <c r="J17" s="3">
-        <v>1230000</v>
+        <v>1226000</v>
       </c>
       <c r="K17" s="3">
         <v>1036500</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>79400</v>
+        <v>169800</v>
       </c>
       <c r="E18" s="3">
-        <v>57100</v>
+        <v>147000</v>
       </c>
       <c r="F18" s="3">
-        <v>150000</v>
+        <v>150600</v>
       </c>
       <c r="G18" s="3">
-        <v>123400</v>
+        <v>141100</v>
       </c>
       <c r="H18" s="3">
-        <v>236400</v>
+        <v>242600</v>
       </c>
       <c r="I18" s="3">
-        <v>231800</v>
+        <v>235600</v>
       </c>
       <c r="J18" s="3">
-        <v>206500</v>
+        <v>210500</v>
       </c>
       <c r="K18" s="3">
         <v>194300</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2400</v>
+        <v>6500</v>
       </c>
       <c r="E20" s="3">
-        <v>-4300</v>
+        <v>4300</v>
       </c>
       <c r="F20" s="3">
-        <v>-6000</v>
+        <v>3600</v>
       </c>
       <c r="G20" s="3">
-        <v>-5900</v>
+        <v>4500</v>
       </c>
       <c r="H20" s="3">
-        <v>-9000</v>
+        <v>9100</v>
       </c>
       <c r="I20" s="3">
-        <v>-7400</v>
+        <v>5800</v>
       </c>
       <c r="J20" s="3">
-        <v>3800</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>200</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>197600</v>
+        <v>275300</v>
       </c>
       <c r="E21" s="3">
-        <v>145000</v>
+        <v>231700</v>
       </c>
       <c r="F21" s="3">
-        <v>235100</v>
+        <v>238100</v>
       </c>
       <c r="G21" s="3">
-        <v>205100</v>
+        <v>224300</v>
       </c>
       <c r="H21" s="3">
-        <v>326500</v>
+        <v>332500</v>
       </c>
       <c r="I21" s="3">
-        <v>318600</v>
+        <v>324000</v>
       </c>
       <c r="J21" s="3">
-        <v>300400</v>
+        <v>300600</v>
       </c>
       <c r="K21" s="3">
         <v>274700</v>
@@ -1275,7 +1275,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>48600</v>
+        <v>58200</v>
       </c>
       <c r="E22" s="3">
         <v>14600</v>
@@ -1380,10 +1380,10 @@
         <v>48500</v>
       </c>
       <c r="I24" s="3">
-        <v>38700</v>
+        <v>41300</v>
       </c>
       <c r="J24" s="3">
-        <v>37100</v>
+        <v>136300</v>
       </c>
       <c r="K24" s="3">
         <v>47000</v>
@@ -1470,10 +1470,10 @@
         <v>158400</v>
       </c>
       <c r="I26" s="3">
-        <v>168800</v>
+        <v>166200</v>
       </c>
       <c r="J26" s="3">
-        <v>158600</v>
+        <v>59400</v>
       </c>
       <c r="K26" s="3">
         <v>135600</v>
@@ -1512,13 +1512,13 @@
         <v>63400</v>
       </c>
       <c r="H27" s="3">
-        <v>158400</v>
+        <v>158300</v>
       </c>
       <c r="I27" s="3">
-        <v>168800</v>
+        <v>166200</v>
       </c>
       <c r="J27" s="3">
-        <v>158600</v>
+        <v>59400</v>
       </c>
       <c r="K27" s="3">
         <v>135600</v>
@@ -1589,26 +1589,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>-2600</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-99200</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2400</v>
+        <v>-6500</v>
       </c>
       <c r="E32" s="3">
-        <v>4300</v>
+        <v>-4300</v>
       </c>
       <c r="F32" s="3">
-        <v>6000</v>
+        <v>-3600</v>
       </c>
       <c r="G32" s="3">
-        <v>5900</v>
+        <v>-4500</v>
       </c>
       <c r="H32" s="3">
-        <v>9000</v>
+        <v>-9100</v>
       </c>
       <c r="I32" s="3">
-        <v>7400</v>
+        <v>-5800</v>
       </c>
       <c r="J32" s="3">
-        <v>-3800</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>-200</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>38100</v>
+        <v>12200</v>
       </c>
       <c r="E45" s="3">
-        <v>37700</v>
+        <v>13300</v>
       </c>
       <c r="F45" s="3">
-        <v>41900</v>
+        <v>13200</v>
       </c>
       <c r="G45" s="3">
-        <v>40700</v>
+        <v>13300</v>
       </c>
       <c r="H45" s="3">
-        <v>66500</v>
+        <v>37900</v>
       </c>
       <c r="I45" s="3">
-        <v>45300</v>
+        <v>18800</v>
       </c>
       <c r="J45" s="3">
-        <v>32500</v>
+        <v>16200</v>
       </c>
       <c r="K45" s="3">
         <v>27200</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>8500</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>61700</v>
+        <v>45500</v>
       </c>
       <c r="E52" s="3">
-        <v>56300</v>
+        <v>29700</v>
       </c>
       <c r="F52" s="3">
-        <v>70100</v>
+        <v>47800</v>
       </c>
       <c r="G52" s="3">
-        <v>59700</v>
+        <v>37600</v>
       </c>
       <c r="H52" s="3">
-        <v>71800</v>
+        <v>50600</v>
       </c>
       <c r="I52" s="3">
-        <v>40200</v>
+        <v>18300</v>
       </c>
       <c r="J52" s="3">
-        <v>40400</v>
+        <v>27600</v>
       </c>
       <c r="K52" s="3">
         <v>38900</v>
@@ -2706,19 +2706,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>10900</v>
+        <v>21800</v>
       </c>
       <c r="E58" s="3">
-        <v>1400</v>
+        <v>11700</v>
       </c>
       <c r="F58" s="3">
-        <v>3700</v>
+        <v>14900</v>
       </c>
       <c r="G58" s="3">
-        <v>4400</v>
+        <v>16100</v>
       </c>
       <c r="H58" s="3">
-        <v>9800</v>
+        <v>20500</v>
       </c>
       <c r="I58" s="3">
         <v>7700</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>221500</v>
+        <v>101800</v>
       </c>
       <c r="E59" s="3">
-        <v>158600</v>
+        <v>68100</v>
       </c>
       <c r="F59" s="3">
-        <v>175600</v>
+        <v>64500</v>
       </c>
       <c r="G59" s="3">
-        <v>178600</v>
+        <v>84900</v>
       </c>
       <c r="H59" s="3">
-        <v>214600</v>
+        <v>101400</v>
       </c>
       <c r="I59" s="3">
-        <v>206800</v>
+        <v>87900</v>
       </c>
       <c r="J59" s="3">
-        <v>181200</v>
+        <v>70900</v>
       </c>
       <c r="K59" s="3">
         <v>157000</v>
@@ -2841,19 +2841,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1280000</v>
+        <v>1321600</v>
       </c>
       <c r="E61" s="3">
-        <v>569600</v>
+        <v>586800</v>
       </c>
       <c r="F61" s="3">
-        <v>599900</v>
+        <v>618000</v>
       </c>
       <c r="G61" s="3">
-        <v>699900</v>
+        <v>716200</v>
       </c>
       <c r="H61" s="3">
-        <v>825000</v>
+        <v>847200</v>
       </c>
       <c r="I61" s="3">
         <v>936400</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>269200</v>
+        <v>60900</v>
       </c>
       <c r="E62" s="3">
-        <v>192700</v>
+        <v>58600</v>
       </c>
       <c r="F62" s="3">
-        <v>237700</v>
+        <v>76200</v>
       </c>
       <c r="G62" s="3">
-        <v>298300</v>
+        <v>92200</v>
       </c>
       <c r="H62" s="3">
-        <v>292900</v>
+        <v>96000</v>
       </c>
       <c r="I62" s="3">
-        <v>311700</v>
+        <v>100800</v>
       </c>
       <c r="J62" s="3">
-        <v>264000</v>
+        <v>101500</v>
       </c>
       <c r="K62" s="3">
         <v>199200</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>115800</v>
+        <v>48300</v>
       </c>
       <c r="E83" s="3">
-        <v>92200</v>
+        <v>44000</v>
       </c>
       <c r="F83" s="3">
-        <v>91100</v>
+        <v>47600</v>
       </c>
       <c r="G83" s="3">
-        <v>87700</v>
+        <v>46600</v>
       </c>
       <c r="H83" s="3">
-        <v>99100</v>
+        <v>47600</v>
       </c>
       <c r="I83" s="3">
-        <v>94200</v>
+        <v>49000</v>
       </c>
       <c r="J83" s="3">
-        <v>90200</v>
+        <v>48900</v>
       </c>
       <c r="K83" s="3">
         <v>80200</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-32400</v>
+        <v>32400</v>
       </c>
       <c r="E96" s="3">
-        <v>-32400</v>
+        <v>32400</v>
       </c>
       <c r="F96" s="3">
-        <v>-32400</v>
+        <v>32400</v>
       </c>
       <c r="G96" s="3">
-        <v>-32400</v>
+        <v>32400</v>
       </c>
       <c r="H96" s="3">
-        <v>-32500</v>
+        <v>32500</v>
       </c>
       <c r="I96" s="3">
-        <v>-32200</v>
+        <v>32200</v>
       </c>
       <c r="J96" s="3">
-        <v>-29600</v>
+        <v>29600</v>
       </c>
       <c r="K96" s="3">
         <v>-27400</v>

--- a/AAII_Financials/Yearly/B_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/B_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
   <si>
     <t>B</t>
   </si>
@@ -656,207 +656,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1450900</v>
+        <v>12922000</v>
       </c>
       <c r="E8" s="3">
-        <v>1261900</v>
+        <v>11397000</v>
       </c>
       <c r="F8" s="3">
-        <v>1258800</v>
+        <v>11013000</v>
       </c>
       <c r="G8" s="3">
-        <v>1124400</v>
+        <v>11985000</v>
       </c>
       <c r="H8" s="3">
-        <v>1491100</v>
+        <v>12595000</v>
       </c>
       <c r="I8" s="3">
-        <v>1495900</v>
+        <v>9717000</v>
       </c>
       <c r="J8" s="3">
+        <v>7243000</v>
+      </c>
+      <c r="K8" s="3">
         <v>1436500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1230800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1194000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1262000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1091600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>928800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>865100</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>995400</v>
+        <v>7961000</v>
       </c>
       <c r="E9" s="3">
-        <v>836800</v>
+        <v>7932000</v>
       </c>
       <c r="F9" s="3">
-        <v>803900</v>
+        <v>7545000</v>
       </c>
       <c r="G9" s="3">
-        <v>721200</v>
+        <v>7110000</v>
       </c>
       <c r="H9" s="3">
-        <v>944200</v>
+        <v>7418000</v>
       </c>
       <c r="I9" s="3">
-        <v>963500</v>
+        <v>6856000</v>
       </c>
       <c r="J9" s="3">
+        <v>5048000</v>
+      </c>
+      <c r="K9" s="3">
         <v>936300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>788700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>782800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>829600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>738200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>655700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>615300</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>455500</v>
+        <v>4961000</v>
       </c>
       <c r="E10" s="3">
-        <v>425100</v>
+        <v>3465000</v>
       </c>
       <c r="F10" s="3">
-        <v>455000</v>
+        <v>3468000</v>
       </c>
       <c r="G10" s="3">
-        <v>403200</v>
+        <v>4875000</v>
       </c>
       <c r="H10" s="3">
-        <v>547000</v>
+        <v>5177000</v>
       </c>
       <c r="I10" s="3">
-        <v>532400</v>
+        <v>2861000</v>
       </c>
       <c r="J10" s="3">
+        <v>2195000</v>
+      </c>
+      <c r="K10" s="3">
         <v>500200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>442000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>411200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>432400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>353400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>273100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>249700</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,34 +888,35 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>13900</v>
-      </c>
-      <c r="E12" s="3">
-        <v>15800</v>
-      </c>
-      <c r="F12" s="3">
-        <v>22900</v>
-      </c>
-      <c r="G12" s="3">
-        <v>16900</v>
+        <v>1000</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H12" s="3">
-        <v>15700</v>
+        <v>1000</v>
       </c>
       <c r="I12" s="3">
-        <v>16200</v>
+        <v>1000</v>
       </c>
       <c r="J12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K12" s="3">
         <v>14800</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
@@ -918,9 +933,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,35 +981,38 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>71900</v>
+        <v>137000</v>
       </c>
       <c r="E14" s="3">
-        <v>89900</v>
+        <v>44000</v>
       </c>
       <c r="F14" s="3">
-        <v>2900</v>
+        <v>918000</v>
       </c>
       <c r="G14" s="3">
-        <v>19200</v>
+        <v>-222000</v>
       </c>
       <c r="H14" s="3">
-        <v>5900</v>
+        <v>-59000</v>
       </c>
       <c r="I14" s="3">
-        <v>5400</v>
+        <v>-3775000</v>
       </c>
       <c r="J14" s="3">
+        <v>941000</v>
+      </c>
+      <c r="K14" s="3">
         <v>200</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
@@ -1008,36 +1029,39 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>112000</v>
+        <v>-594000</v>
       </c>
       <c r="E15" s="3">
-        <v>89000</v>
+        <v>268000</v>
       </c>
       <c r="F15" s="3">
-        <v>91100</v>
+        <v>454000</v>
       </c>
       <c r="G15" s="3">
-        <v>87700</v>
+        <v>12000</v>
       </c>
       <c r="H15" s="3">
-        <v>99100</v>
+        <v>-417000</v>
       </c>
       <c r="I15" s="3">
-        <v>94200</v>
+        <v>-433000</v>
       </c>
       <c r="J15" s="3">
+        <v>278000</v>
+      </c>
+      <c r="K15" s="3">
         <v>90200</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1053,9 +1077,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1097,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1281000</v>
+        <v>8164000</v>
       </c>
       <c r="E17" s="3">
-        <v>1114900</v>
+        <v>8529000</v>
       </c>
       <c r="F17" s="3">
-        <v>1108300</v>
+        <v>8424000</v>
       </c>
       <c r="G17" s="3">
-        <v>983300</v>
+        <v>7700000</v>
       </c>
       <c r="H17" s="3">
-        <v>1248600</v>
+        <v>7676000</v>
       </c>
       <c r="I17" s="3">
-        <v>1260300</v>
+        <v>6820000</v>
       </c>
       <c r="J17" s="3">
+        <v>6042000</v>
+      </c>
+      <c r="K17" s="3">
         <v>1226000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1036500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1025600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1082000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>968400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>821600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>763500</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>169800</v>
+        <v>4758000</v>
       </c>
       <c r="E18" s="3">
-        <v>147000</v>
+        <v>2868000</v>
       </c>
       <c r="F18" s="3">
-        <v>150600</v>
+        <v>2589000</v>
       </c>
       <c r="G18" s="3">
-        <v>141100</v>
+        <v>4285000</v>
       </c>
       <c r="H18" s="3">
-        <v>242600</v>
+        <v>4919000</v>
       </c>
       <c r="I18" s="3">
-        <v>235600</v>
+        <v>2897000</v>
       </c>
       <c r="J18" s="3">
+        <v>1201000</v>
+      </c>
+      <c r="K18" s="3">
         <v>210500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>194300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>168400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>180000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>123200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>107100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>101600</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,233 +1213,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>6500</v>
+        <v>-112000</v>
       </c>
       <c r="E20" s="3">
-        <v>4300</v>
+        <v>-50000</v>
       </c>
       <c r="F20" s="3">
-        <v>3600</v>
+        <v>-241000</v>
       </c>
       <c r="G20" s="3">
-        <v>4500</v>
+        <v>-415000</v>
       </c>
       <c r="H20" s="3">
-        <v>9100</v>
+        <v>-244000</v>
       </c>
       <c r="I20" s="3">
-        <v>5800</v>
+        <v>-63000</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>86000</v>
       </c>
       <c r="K20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3">
         <v>200</v>
       </c>
       <c r="M20" s="3">
+        <v>200</v>
+      </c>
+      <c r="N20" s="3">
         <v>-2100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-300</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>275300</v>
+        <v>4276000</v>
       </c>
       <c r="E21" s="3">
-        <v>231700</v>
+        <v>3186000</v>
       </c>
       <c r="F21" s="3">
-        <v>238100</v>
+        <v>3284000</v>
       </c>
       <c r="G21" s="3">
-        <v>224300</v>
+        <v>4712000</v>
       </c>
       <c r="H21" s="3">
-        <v>332500</v>
+        <v>4746000</v>
       </c>
       <c r="I21" s="3">
-        <v>324000</v>
+        <v>2527000</v>
       </c>
       <c r="J21" s="3">
+        <v>1393000</v>
+      </c>
+      <c r="K21" s="3">
         <v>300600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>274700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>246900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>259300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>185700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>161900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>160200</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>58200</v>
+        <v>423000</v>
       </c>
       <c r="E22" s="3">
+        <v>350000</v>
+      </c>
+      <c r="F22" s="3">
+        <v>341000</v>
+      </c>
+      <c r="G22" s="3">
+        <v>346000</v>
+      </c>
+      <c r="H22" s="3">
+        <v>323000</v>
+      </c>
+      <c r="I22" s="3">
+        <v>427000</v>
+      </c>
+      <c r="J22" s="3">
+        <v>443000</v>
+      </c>
+      <c r="K22" s="3">
         <v>14600</v>
       </c>
-      <c r="F22" s="3">
-        <v>16200</v>
-      </c>
-      <c r="G22" s="3">
-        <v>15900</v>
-      </c>
-      <c r="H22" s="3">
-        <v>20600</v>
-      </c>
-      <c r="I22" s="3">
-        <v>16800</v>
-      </c>
-      <c r="J22" s="3">
-        <v>14600</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>11900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>10700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>11400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>13100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>12200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>10300</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>33300</v>
+        <v>4608000</v>
       </c>
       <c r="E23" s="3">
-        <v>38200</v>
+        <v>2814000</v>
       </c>
       <c r="F23" s="3">
-        <v>127800</v>
+        <v>1681000</v>
       </c>
       <c r="G23" s="3">
-        <v>101500</v>
+        <v>4632000</v>
       </c>
       <c r="H23" s="3">
-        <v>206800</v>
+        <v>4946000</v>
       </c>
       <c r="I23" s="3">
-        <v>207500</v>
+        <v>6357000</v>
       </c>
       <c r="J23" s="3">
+        <v>-237000</v>
+      </c>
+      <c r="K23" s="3">
         <v>195700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>182600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>157900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>166500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>107600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>92300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>91000</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>17300</v>
+        <v>1520000</v>
       </c>
       <c r="E24" s="3">
-        <v>24700</v>
+        <v>861000</v>
       </c>
       <c r="F24" s="3">
-        <v>27900</v>
+        <v>664000</v>
       </c>
       <c r="G24" s="3">
-        <v>38100</v>
+        <v>1344000</v>
       </c>
       <c r="H24" s="3">
-        <v>48500</v>
+        <v>1332000</v>
       </c>
       <c r="I24" s="3">
-        <v>41300</v>
+        <v>1783000</v>
       </c>
       <c r="J24" s="3">
+        <v>1198000</v>
+      </c>
+      <c r="K24" s="3">
         <v>136300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>47000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>36600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>46000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>35300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>12400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>16000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1498,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>16000</v>
+        <v>3088000</v>
       </c>
       <c r="E26" s="3">
-        <v>13500</v>
+        <v>1953000</v>
       </c>
       <c r="F26" s="3">
-        <v>99900</v>
+        <v>1017000</v>
       </c>
       <c r="G26" s="3">
-        <v>63400</v>
+        <v>3288000</v>
       </c>
       <c r="H26" s="3">
-        <v>158400</v>
+        <v>3614000</v>
       </c>
       <c r="I26" s="3">
-        <v>166200</v>
+        <v>4574000</v>
       </c>
       <c r="J26" s="3">
+        <v>-1435000</v>
+      </c>
+      <c r="K26" s="3">
         <v>59400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>135600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>121400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>120500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>72300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>79800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>75000</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>16000</v>
+        <v>2144000</v>
       </c>
       <c r="E27" s="3">
-        <v>13500</v>
+        <v>1272000</v>
       </c>
       <c r="F27" s="3">
-        <v>99900</v>
+        <v>432000</v>
       </c>
       <c r="G27" s="3">
-        <v>63400</v>
+        <v>2022000</v>
       </c>
       <c r="H27" s="3">
-        <v>158300</v>
+        <v>2324000</v>
       </c>
       <c r="I27" s="3">
-        <v>166200</v>
+        <v>3969000</v>
       </c>
       <c r="J27" s="3">
+        <v>-1545000</v>
+      </c>
+      <c r="K27" s="3">
         <v>59400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>135600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>121400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>120500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>72300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>79800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>75000</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1642,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1617,20 +1679,23 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-2200</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>198200</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>15400</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1786,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-6500</v>
+        <v>112000</v>
       </c>
       <c r="E32" s="3">
-        <v>-4300</v>
+        <v>50000</v>
       </c>
       <c r="F32" s="3">
-        <v>-3600</v>
+        <v>241000</v>
       </c>
       <c r="G32" s="3">
-        <v>-4500</v>
+        <v>415000</v>
       </c>
       <c r="H32" s="3">
-        <v>-9100</v>
+        <v>244000</v>
       </c>
       <c r="I32" s="3">
-        <v>-5800</v>
+        <v>63000</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>-86000</v>
       </c>
       <c r="K32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3">
         <v>-200</v>
       </c>
       <c r="M32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N32" s="3">
         <v>2100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>300</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>16000</v>
+        <v>2144000</v>
       </c>
       <c r="E33" s="3">
-        <v>13500</v>
+        <v>1272000</v>
       </c>
       <c r="F33" s="3">
-        <v>99900</v>
+        <v>432000</v>
       </c>
       <c r="G33" s="3">
-        <v>63400</v>
+        <v>2022000</v>
       </c>
       <c r="H33" s="3">
-        <v>158400</v>
+        <v>2324000</v>
       </c>
       <c r="I33" s="3">
-        <v>166200</v>
+        <v>3969000</v>
       </c>
       <c r="J33" s="3">
+        <v>-1545000</v>
+      </c>
+      <c r="K33" s="3">
         <v>59400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>135600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>121400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>118400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>270500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>95200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>64700</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1930,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>16000</v>
+        <v>2144000</v>
       </c>
       <c r="E35" s="3">
-        <v>13500</v>
+        <v>1272000</v>
       </c>
       <c r="F35" s="3">
-        <v>99900</v>
+        <v>432000</v>
       </c>
       <c r="G35" s="3">
-        <v>63400</v>
+        <v>2022000</v>
       </c>
       <c r="H35" s="3">
-        <v>158400</v>
+        <v>2324000</v>
       </c>
       <c r="I35" s="3">
-        <v>166200</v>
+        <v>3969000</v>
       </c>
       <c r="J35" s="3">
+        <v>-1545000</v>
+      </c>
+      <c r="K35" s="3">
         <v>59400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>135600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>121400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>118400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>270500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>95200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>64700</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,53 +2074,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>89800</v>
+        <v>4074000</v>
       </c>
       <c r="E41" s="3">
-        <v>76900</v>
+        <v>4148000</v>
       </c>
       <c r="F41" s="3">
-        <v>102900</v>
+        <v>4440000</v>
       </c>
       <c r="G41" s="3">
-        <v>79100</v>
+        <v>5280000</v>
       </c>
       <c r="H41" s="3">
-        <v>93800</v>
+        <v>5188000</v>
       </c>
       <c r="I41" s="3">
-        <v>100700</v>
+        <v>3314000</v>
       </c>
       <c r="J41" s="3">
+        <v>1571000</v>
+      </c>
+      <c r="K41" s="3">
         <v>145300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>66400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>83900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>46000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>70900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>86400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>62500</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2076,216 +2167,231 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>413600</v>
+        <v>1363000</v>
       </c>
       <c r="E43" s="3">
-        <v>334300</v>
+        <v>1178000</v>
       </c>
       <c r="F43" s="3">
-        <v>295800</v>
+        <v>906000</v>
       </c>
       <c r="G43" s="3">
-        <v>284500</v>
+        <v>942000</v>
       </c>
       <c r="H43" s="3">
-        <v>371400</v>
+        <v>766000</v>
       </c>
       <c r="I43" s="3">
-        <v>394100</v>
+        <v>665000</v>
       </c>
       <c r="J43" s="3">
+        <v>430000</v>
+      </c>
+      <c r="K43" s="3">
         <v>348900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>287100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>261800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>275900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>258700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>253200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>200500</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>365200</v>
+        <v>1942000</v>
       </c>
       <c r="E44" s="3">
-        <v>283400</v>
+        <v>1782000</v>
       </c>
       <c r="F44" s="3">
-        <v>239700</v>
+        <v>1781000</v>
       </c>
       <c r="G44" s="3">
-        <v>238000</v>
+        <v>1734000</v>
       </c>
       <c r="H44" s="3">
-        <v>232700</v>
+        <v>1878000</v>
       </c>
       <c r="I44" s="3">
-        <v>266000</v>
+        <v>2289000</v>
       </c>
       <c r="J44" s="3">
+        <v>1852000</v>
+      </c>
+      <c r="K44" s="3">
         <v>242000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>227800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>208600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>212000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>211200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>226200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>216500</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>12200</v>
+        <v>103000</v>
       </c>
       <c r="E45" s="3">
-        <v>13300</v>
+        <v>127000</v>
       </c>
       <c r="F45" s="3">
-        <v>13200</v>
+        <v>150000</v>
       </c>
       <c r="G45" s="3">
-        <v>13300</v>
+        <v>87000</v>
       </c>
       <c r="H45" s="3">
-        <v>37900</v>
+        <v>84000</v>
       </c>
       <c r="I45" s="3">
-        <v>18800</v>
+        <v>445000</v>
       </c>
       <c r="J45" s="3">
+        <v>53000</v>
+      </c>
+      <c r="K45" s="3">
         <v>16200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>27200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>57300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>54400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>36400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>71600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>50500</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>906700</v>
+        <v>7632000</v>
       </c>
       <c r="E46" s="3">
-        <v>732300</v>
+        <v>7438000</v>
       </c>
       <c r="F46" s="3">
-        <v>680200</v>
+        <v>8465000</v>
       </c>
       <c r="G46" s="3">
-        <v>642300</v>
+        <v>8249000</v>
       </c>
       <c r="H46" s="3">
-        <v>764400</v>
+        <v>8143000</v>
       </c>
       <c r="I46" s="3">
-        <v>806100</v>
+        <v>6887000</v>
       </c>
       <c r="J46" s="3">
+        <v>3978000</v>
+      </c>
+      <c r="K46" s="3">
         <v>768700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>608500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>611600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>588400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>577200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>618500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>530000</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>6000</v>
+        <v>4154000</v>
       </c>
       <c r="E47" s="3">
-        <v>8500</v>
+        <v>4264000</v>
       </c>
       <c r="F47" s="3">
-        <v>300</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
+        <v>4095000</v>
+      </c>
+      <c r="G47" s="3">
+        <v>5008000</v>
+      </c>
+      <c r="H47" s="3">
+        <v>5098000</v>
       </c>
       <c r="I47" s="3">
-        <v>1400</v>
+        <v>4785000</v>
       </c>
       <c r="J47" s="3">
+        <v>1444000</v>
+      </c>
+      <c r="K47" s="3">
         <v>700</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -2301,99 +2407,108 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>449500</v>
+        <v>28559000</v>
       </c>
       <c r="E48" s="3">
-        <v>347200</v>
+        <v>26416000</v>
       </c>
       <c r="F48" s="3">
-        <v>370900</v>
+        <v>25821000</v>
       </c>
       <c r="G48" s="3">
-        <v>398500</v>
+        <v>24954000</v>
       </c>
       <c r="H48" s="3">
-        <v>388000</v>
+        <v>24628000</v>
       </c>
       <c r="I48" s="3">
-        <v>370500</v>
+        <v>24141000</v>
       </c>
       <c r="J48" s="3">
+        <v>12826000</v>
+      </c>
+      <c r="K48" s="3">
         <v>359300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>334500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>308900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>299400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>302600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>233100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>210800</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1890100</v>
+        <v>3245000</v>
       </c>
       <c r="E49" s="3">
-        <v>1278000</v>
+        <v>3730000</v>
       </c>
       <c r="F49" s="3">
-        <v>1455600</v>
+        <v>3730000</v>
       </c>
       <c r="G49" s="3">
-        <v>1575700</v>
+        <v>4919000</v>
       </c>
       <c r="H49" s="3">
-        <v>1514100</v>
+        <v>4938000</v>
       </c>
       <c r="I49" s="3">
-        <v>1592100</v>
+        <v>4995000</v>
       </c>
       <c r="J49" s="3">
+        <v>1403000</v>
+      </c>
+      <c r="K49" s="3">
         <v>1197300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1155700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1116300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1149600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1184000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>930100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>638200</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2599,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>45500</v>
+        <v>3819000</v>
       </c>
       <c r="E52" s="3">
-        <v>29700</v>
+        <v>3776000</v>
       </c>
       <c r="F52" s="3">
-        <v>47800</v>
+        <v>3675000</v>
       </c>
       <c r="G52" s="3">
-        <v>37600</v>
+        <v>3608000</v>
       </c>
       <c r="H52" s="3">
-        <v>50600</v>
+        <v>3447000</v>
       </c>
       <c r="I52" s="3">
-        <v>18300</v>
+        <v>3147000</v>
       </c>
       <c r="J52" s="3">
+        <v>2436000</v>
+      </c>
+      <c r="K52" s="3">
         <v>27600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>38900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>25100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>36400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>59900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>53100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>61400</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2695,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3308000</v>
+        <v>47626000</v>
       </c>
       <c r="E54" s="3">
-        <v>2413700</v>
+        <v>45811000</v>
       </c>
       <c r="F54" s="3">
-        <v>2576800</v>
+        <v>45965000</v>
       </c>
       <c r="G54" s="3">
-        <v>2676200</v>
+        <v>46890000</v>
       </c>
       <c r="H54" s="3">
-        <v>2738300</v>
+        <v>46506000</v>
       </c>
       <c r="I54" s="3">
-        <v>2809000</v>
+        <v>44392000</v>
       </c>
       <c r="J54" s="3">
+        <v>22631000</v>
+      </c>
+      <c r="K54" s="3">
         <v>2365700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2137500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2061900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2073900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2123700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1868600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1440400</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2786,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>164300</v>
+        <v>655000</v>
       </c>
       <c r="E57" s="3">
-        <v>145100</v>
+        <v>678000</v>
       </c>
       <c r="F57" s="3">
-        <v>131100</v>
+        <v>1686000</v>
       </c>
       <c r="G57" s="3">
-        <v>112400</v>
+        <v>539000</v>
       </c>
       <c r="H57" s="3">
-        <v>118500</v>
+        <v>929000</v>
       </c>
       <c r="I57" s="3">
-        <v>143400</v>
+        <v>715000</v>
       </c>
       <c r="J57" s="3">
+        <v>744000</v>
+      </c>
+      <c r="K57" s="3">
         <v>127500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>112000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>97000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>94800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>88700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>99000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>92500</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>21800</v>
+        <v>84000</v>
       </c>
       <c r="E58" s="3">
-        <v>11700</v>
+        <v>43000</v>
       </c>
       <c r="F58" s="3">
-        <v>14900</v>
+        <v>45000</v>
       </c>
       <c r="G58" s="3">
-        <v>16100</v>
+        <v>24000</v>
       </c>
       <c r="H58" s="3">
-        <v>20500</v>
+        <v>20000</v>
       </c>
       <c r="I58" s="3">
-        <v>7700</v>
+        <v>375000</v>
       </c>
       <c r="J58" s="3">
+        <v>43000</v>
+      </c>
+      <c r="K58" s="3">
         <v>7000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>32900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>24200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>8900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>57100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>12900</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>101800</v>
+        <v>891000</v>
       </c>
       <c r="E59" s="3">
-        <v>68100</v>
+        <v>760000</v>
       </c>
       <c r="F59" s="3">
-        <v>64500</v>
+        <v>524000</v>
       </c>
       <c r="G59" s="3">
-        <v>84900</v>
+        <v>557000</v>
       </c>
       <c r="H59" s="3">
-        <v>101400</v>
+        <v>675000</v>
       </c>
       <c r="I59" s="3">
-        <v>87900</v>
+        <v>798000</v>
       </c>
       <c r="J59" s="3">
+        <v>494000</v>
+      </c>
+      <c r="K59" s="3">
         <v>70900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>157000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>131300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>161400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>154500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>149500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>92300</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>396600</v>
+        <v>2642000</v>
       </c>
       <c r="E60" s="3">
-        <v>305100</v>
+        <v>2356000</v>
       </c>
       <c r="F60" s="3">
-        <v>310400</v>
+        <v>3120000</v>
       </c>
       <c r="G60" s="3">
-        <v>295400</v>
+        <v>2086000</v>
       </c>
       <c r="H60" s="3">
-        <v>342900</v>
+        <v>2220000</v>
       </c>
       <c r="I60" s="3">
-        <v>357900</v>
+        <v>2376000</v>
       </c>
       <c r="J60" s="3">
+        <v>1668000</v>
+      </c>
+      <c r="K60" s="3">
         <v>315800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>301900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>252600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>265100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>300300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>199900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>197700</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1321600</v>
+        <v>5172000</v>
       </c>
       <c r="E61" s="3">
-        <v>586800</v>
+        <v>5180000</v>
       </c>
       <c r="F61" s="3">
-        <v>618000</v>
+        <v>5205000</v>
       </c>
       <c r="G61" s="3">
-        <v>716200</v>
+        <v>5449000</v>
       </c>
       <c r="H61" s="3">
-        <v>847200</v>
+        <v>5344000</v>
       </c>
       <c r="I61" s="3">
-        <v>936400</v>
+        <v>5161000</v>
       </c>
       <c r="J61" s="3">
+        <v>5695000</v>
+      </c>
+      <c r="K61" s="3">
         <v>525600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>468100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>485700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>495800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>490300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>642100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>333100</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>60900</v>
+        <v>2028000</v>
       </c>
       <c r="E62" s="3">
-        <v>58600</v>
+        <v>2202000</v>
       </c>
       <c r="F62" s="3">
-        <v>76200</v>
+        <v>2449000</v>
       </c>
       <c r="G62" s="3">
-        <v>92200</v>
+        <v>3073000</v>
       </c>
       <c r="H62" s="3">
-        <v>96000</v>
+        <v>3534000</v>
       </c>
       <c r="I62" s="3">
-        <v>100800</v>
+        <v>3450000</v>
       </c>
       <c r="J62" s="3">
+        <v>3346000</v>
+      </c>
+      <c r="K62" s="3">
         <v>101500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>199200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>195900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>201200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>191600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>226500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>187100</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3215,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1945800</v>
+        <v>14370000</v>
       </c>
       <c r="E66" s="3">
-        <v>1067400</v>
+        <v>13809000</v>
       </c>
       <c r="F66" s="3">
-        <v>1148100</v>
+        <v>14676000</v>
       </c>
       <c r="G66" s="3">
-        <v>1293500</v>
+        <v>14583000</v>
       </c>
       <c r="H66" s="3">
-        <v>1467800</v>
+        <v>14796000</v>
       </c>
       <c r="I66" s="3">
-        <v>1605900</v>
+        <v>14565000</v>
       </c>
       <c r="J66" s="3">
+        <v>13246000</v>
+      </c>
+      <c r="K66" s="3">
         <v>1105400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>969200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>934100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>962100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>982300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1068500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>718000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3475,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1551200</v>
+        <v>-5269000</v>
       </c>
       <c r="E72" s="3">
-        <v>1567900</v>
+        <v>-6713000</v>
       </c>
       <c r="F72" s="3">
-        <v>1587000</v>
+        <v>-7282000</v>
       </c>
       <c r="G72" s="3">
-        <v>1519800</v>
+        <v>-6566000</v>
       </c>
       <c r="H72" s="3">
-        <v>1489200</v>
+        <v>-7949000</v>
       </c>
       <c r="I72" s="3">
-        <v>1363800</v>
+        <v>-9722000</v>
       </c>
       <c r="J72" s="3">
+        <v>-13453000</v>
+      </c>
+      <c r="K72" s="3">
         <v>1206700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1177200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1069200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>974500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>881200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>633400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>560200</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3667,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1362300</v>
+        <v>24290000</v>
       </c>
       <c r="E76" s="3">
-        <v>1346300</v>
+        <v>23341000</v>
       </c>
       <c r="F76" s="3">
-        <v>1428800</v>
+        <v>22771000</v>
       </c>
       <c r="G76" s="3">
-        <v>1382700</v>
+        <v>23857000</v>
       </c>
       <c r="H76" s="3">
-        <v>1270500</v>
+        <v>23341000</v>
       </c>
       <c r="I76" s="3">
-        <v>1203100</v>
+        <v>21432000</v>
       </c>
       <c r="J76" s="3">
+        <v>7593000</v>
+      </c>
+      <c r="K76" s="3">
         <v>1260300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1168400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1127800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1111800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1141400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>800100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>722400</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3763,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>16000</v>
+        <v>2144000</v>
       </c>
       <c r="E81" s="3">
-        <v>13500</v>
+        <v>1272000</v>
       </c>
       <c r="F81" s="3">
-        <v>99900</v>
+        <v>432000</v>
       </c>
       <c r="G81" s="3">
-        <v>63400</v>
+        <v>2022000</v>
       </c>
       <c r="H81" s="3">
-        <v>158400</v>
+        <v>2324000</v>
       </c>
       <c r="I81" s="3">
-        <v>166200</v>
+        <v>3969000</v>
       </c>
       <c r="J81" s="3">
+        <v>-1545000</v>
+      </c>
+      <c r="K81" s="3">
         <v>59400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>135600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>121400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>118400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>270500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>95200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>64700</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3887,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>48300</v>
+        <v>1914000</v>
       </c>
       <c r="E83" s="3">
-        <v>44000</v>
+        <v>2043000</v>
       </c>
       <c r="F83" s="3">
-        <v>47600</v>
+        <v>1996000</v>
       </c>
       <c r="G83" s="3">
-        <v>46600</v>
+        <v>2099000</v>
       </c>
       <c r="H83" s="3">
-        <v>47600</v>
+        <v>2192000</v>
       </c>
       <c r="I83" s="3">
-        <v>49000</v>
+        <v>2030000</v>
       </c>
       <c r="J83" s="3">
+        <v>1453000</v>
+      </c>
+      <c r="K83" s="3">
         <v>48900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>80200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>78200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>81400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>65100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>57400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>58900</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4172,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>112400</v>
+        <v>4491000</v>
       </c>
       <c r="E89" s="3">
-        <v>75600</v>
+        <v>3732000</v>
       </c>
       <c r="F89" s="3">
-        <v>167800</v>
+        <v>3481000</v>
       </c>
       <c r="G89" s="3">
-        <v>215500</v>
+        <v>4378000</v>
       </c>
       <c r="H89" s="3">
-        <v>248300</v>
+        <v>5417000</v>
       </c>
       <c r="I89" s="3">
-        <v>237200</v>
+        <v>2833000</v>
       </c>
       <c r="J89" s="3">
+        <v>1765000</v>
+      </c>
+      <c r="K89" s="3">
         <v>203900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>217600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>217500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>186900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>10100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>136400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>121000</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4243,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-55700</v>
+        <v>-3174000</v>
       </c>
       <c r="E91" s="3">
-        <v>-35100</v>
+        <v>-3086000</v>
       </c>
       <c r="F91" s="3">
-        <v>-34100</v>
+        <v>-3049000</v>
       </c>
       <c r="G91" s="3">
-        <v>-40700</v>
+        <v>-2435000</v>
       </c>
       <c r="H91" s="3">
-        <v>-53300</v>
+        <v>-2054000</v>
       </c>
       <c r="I91" s="3">
+        <v>-1701000</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-1400000</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-58700</v>
+      </c>
+      <c r="L91" s="3">
+        <v>-47600</v>
+      </c>
+      <c r="M91" s="3">
+        <v>-46000</v>
+      </c>
+      <c r="N91" s="3">
+        <v>-57400</v>
+      </c>
+      <c r="O91" s="3">
         <v>-57300</v>
       </c>
-      <c r="J91" s="3">
-        <v>-58700</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-47600</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-46000</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-57400</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-57300</v>
-      </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-37800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-37100</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4384,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-767500</v>
+        <v>-2764000</v>
       </c>
       <c r="E94" s="3">
-        <v>-36000</v>
+        <v>-2816000</v>
       </c>
       <c r="F94" s="3">
-        <v>-29800</v>
+        <v>-1711000</v>
       </c>
       <c r="G94" s="3">
-        <v>-4200</v>
+        <v>-1897000</v>
       </c>
       <c r="H94" s="3">
-        <v>-62200</v>
+        <v>-1286000</v>
       </c>
       <c r="I94" s="3">
-        <v>-493200</v>
+        <v>50000</v>
       </c>
       <c r="J94" s="3">
+        <v>-1494000</v>
+      </c>
+      <c r="K94" s="3">
         <v>-68000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-179500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-115500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-124200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>157400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-332800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-30600</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,53 +4455,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>32400</v>
+        <v>696000</v>
       </c>
       <c r="E96" s="3">
-        <v>32400</v>
+        <v>700000</v>
       </c>
       <c r="F96" s="3">
-        <v>32400</v>
+        <v>1143000</v>
       </c>
       <c r="G96" s="3">
-        <v>32400</v>
+        <v>634000</v>
       </c>
       <c r="H96" s="3">
-        <v>32500</v>
+        <v>547000</v>
       </c>
       <c r="I96" s="3">
-        <v>32200</v>
+        <v>548000</v>
       </c>
       <c r="J96" s="3">
+        <v>125000</v>
+      </c>
+      <c r="K96" s="3">
         <v>29600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-27400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-26200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-24500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-22400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-21700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-18600</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4644,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>666600</v>
+        <v>-1795000</v>
       </c>
       <c r="E100" s="3">
-        <v>-64800</v>
+        <v>-1205000</v>
       </c>
       <c r="F100" s="3">
-        <v>-114700</v>
+        <v>-2604000</v>
       </c>
       <c r="G100" s="3">
-        <v>-219700</v>
+        <v>-2388000</v>
       </c>
       <c r="H100" s="3">
-        <v>-192000</v>
+        <v>-2254000</v>
       </c>
       <c r="I100" s="3">
-        <v>215600</v>
+        <v>-1139000</v>
       </c>
       <c r="J100" s="3">
+        <v>-925000</v>
+      </c>
+      <c r="K100" s="3">
         <v>-63800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-53300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-59200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-83500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-182800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>219300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-40200</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-500</v>
+        <v>-6000</v>
       </c>
       <c r="E101" s="3">
-        <v>-5500</v>
+        <v>-3000</v>
       </c>
       <c r="F101" s="3">
-        <v>-2900</v>
+        <v>-6000</v>
       </c>
       <c r="G101" s="3">
-        <v>6100</v>
+        <v>-1000</v>
       </c>
       <c r="H101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I101" s="3">
         <v>-1000</v>
       </c>
-      <c r="I101" s="3">
-        <v>-4100</v>
-      </c>
       <c r="J101" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="K101" s="3">
         <v>6700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>10900</v>
+        <v>-74000</v>
       </c>
       <c r="E102" s="3">
-        <v>-30800</v>
+        <v>-292000</v>
       </c>
       <c r="F102" s="3">
-        <v>20400</v>
+        <v>-840000</v>
       </c>
       <c r="G102" s="3">
-        <v>-2300</v>
+        <v>92000</v>
       </c>
       <c r="H102" s="3">
-        <v>-6900</v>
+        <v>1874000</v>
       </c>
       <c r="I102" s="3">
-        <v>-44600</v>
+        <v>1743000</v>
       </c>
       <c r="J102" s="3">
+        <v>-663000</v>
+      </c>
+      <c r="K102" s="3">
         <v>78800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-17500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>37900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-24800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-15500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>23900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>49100</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/B_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/B_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
   <si>
     <t>B</t>
   </si>
@@ -656,221 +656,233 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>16956000</v>
+      </c>
+      <c r="E8" s="3">
         <v>12922000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>11397000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11013000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>11985000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>12595000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9717000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7243000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1436500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1230800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1194000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1262000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1091600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>928800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>865100</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>8265000</v>
+      </c>
+      <c r="E9" s="3">
         <v>7961000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7932000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7545000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7110000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7418000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6856000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5048000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>936300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>788700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>782800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>829600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>738200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>655700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>615300</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>8691000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4961000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3465000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3468000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4875000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5177000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2861000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2195000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>500200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>442000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>411200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>432400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>353400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>273100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>249700</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -889,16 +901,17 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>1000</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -906,8 +919,8 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
-        <v>1000</v>
+      <c r="H12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I12" s="3">
         <v>1000</v>
@@ -916,10 +929,10 @@
         <v>1000</v>
       </c>
       <c r="K12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L12" s="3">
         <v>14800</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -936,9 +949,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,38 +1000,41 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>137000</v>
+        <v>-541000</v>
       </c>
       <c r="E14" s="3">
+        <v>180000</v>
+      </c>
+      <c r="F14" s="3">
         <v>44000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>918000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-222000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-59000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-3775000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>941000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>200</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
@@ -1032,39 +1051,42 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E15" s="3">
         <v>-594000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>268000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>454000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>12000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>-417000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>-433000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>278000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>90200</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1080,9 +1102,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1098,104 +1123,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8164000</v>
+        <v>9040000</v>
       </c>
       <c r="E17" s="3">
+        <v>8210000</v>
+      </c>
+      <c r="F17" s="3">
         <v>8529000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8424000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7700000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7676000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6820000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6042000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1226000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1036500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1025600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1082000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>968400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>821600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>763500</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4758000</v>
+        <v>7916000</v>
       </c>
       <c r="E18" s="3">
+        <v>4712000</v>
+      </c>
+      <c r="F18" s="3">
         <v>2868000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2589000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4285000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4919000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2897000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1201000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>210500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>194300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>168400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>180000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>123200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>107100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>101600</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1214,248 +1246,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-112000</v>
+        <v>-441000</v>
       </c>
       <c r="E20" s="3">
+        <v>-202000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-50000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-241000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-415000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-244000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-63000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>86000</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M20" s="3">
         <v>200</v>
       </c>
       <c r="N20" s="3">
+        <v>200</v>
+      </c>
+      <c r="O20" s="3">
         <v>-2100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4276000</v>
+        <v>8365000</v>
       </c>
       <c r="E21" s="3">
+        <v>4320000</v>
+      </c>
+      <c r="F21" s="3">
         <v>3186000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3284000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4712000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4746000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2527000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1393000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>300600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>274700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>246900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>259300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>185700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>161900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>160200</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>358000</v>
+      </c>
+      <c r="E22" s="3">
         <v>423000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>350000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>341000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>346000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>323000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>427000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>443000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>11900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>10700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>11400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>13100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>12200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>10300</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8805000</v>
+      </c>
+      <c r="E23" s="3">
         <v>4608000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2814000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1681000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4632000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4946000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6357000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-237000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>195700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>182600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>157900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>166500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>107600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>92300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>91000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1651000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1520000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>861000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>664000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1344000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1332000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1783000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1198000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>136300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>47000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>36600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>46000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>35300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>12400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>16000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1501,105 +1549,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7154000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3088000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1953000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1017000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3288000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3614000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4574000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1435000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>59400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>135600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>121400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>120500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>72300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>79800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>75000</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4993000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2144000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1272000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>432000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2022000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2324000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3969000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1545000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>59400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>135600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>121400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>120500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>72300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>79800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>75000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1645,9 +1702,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1682,20 +1742,23 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-2200</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>198200</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>15400</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-10200</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1741,9 +1804,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1789,105 +1855,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>112000</v>
+        <v>441000</v>
       </c>
       <c r="E32" s="3">
+        <v>202000</v>
+      </c>
+      <c r="F32" s="3">
         <v>50000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>241000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>415000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>244000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>63000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-86000</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="M32" s="3">
         <v>-200</v>
       </c>
       <c r="N32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O32" s="3">
         <v>2100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4993000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2144000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1272000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>432000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2022000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2324000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3969000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1545000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>59400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>135600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>121400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>118400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>270500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>95200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>64700</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1933,110 +2008,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4993000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2144000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1272000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>432000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2022000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2324000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3969000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1545000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>59400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>135600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>121400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>118400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>270500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>95200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>64700</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2055,8 +2139,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2075,56 +2160,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6706000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4074000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4148000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4440000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5280000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5188000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3314000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1571000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>145300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>66400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>83900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>46000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>70900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>86400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>62500</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2170,231 +2259,246 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1123000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1363000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1178000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>906000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>942000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>766000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>665000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>430000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>348900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>287100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>261800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>275900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>258700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>253200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>200500</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2068000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1942000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1782000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1781000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1734000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1878000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2289000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1852000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>242000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>227800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>208600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>212000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>211200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>226200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>216500</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>128000</v>
+      </c>
+      <c r="E45" s="3">
         <v>103000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>127000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>150000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>87000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>84000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>445000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>53000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>16200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>27200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>57300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>54400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>36400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>71600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>50500</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10217000</v>
+      </c>
+      <c r="E46" s="3">
         <v>7632000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7438000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8465000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8249000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8143000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6887000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3978000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>768700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>608500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>611600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>588400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>577200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>618500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>530000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4347000</v>
+      </c>
+      <c r="E47" s="3">
         <v>4154000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4264000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4095000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5008000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5098000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4785000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1444000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>700</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -2410,105 +2514,114 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>29354000</v>
+      </c>
+      <c r="E48" s="3">
         <v>28559000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26416000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>25821000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>24954000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>24628000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>24141000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12826000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>359300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>334500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>308900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>299400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>302600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>233100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>210800</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3182000</v>
+      </c>
+      <c r="E49" s="3">
         <v>3245000</v>
-      </c>
-      <c r="E49" s="3">
-        <v>3730000</v>
       </c>
       <c r="F49" s="3">
         <v>3730000</v>
       </c>
       <c r="G49" s="3">
+        <v>3730000</v>
+      </c>
+      <c r="H49" s="3">
         <v>4919000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4938000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4995000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1403000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1197300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1155700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1116300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1149600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1184000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>930100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>638200</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2554,9 +2667,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2602,57 +2718,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4187000</v>
+      </c>
+      <c r="E52" s="3">
         <v>3819000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3776000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3675000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3608000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3447000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3147000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2436000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>27600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>38900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>25100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>36400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>59900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>53100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>61400</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2698,57 +2820,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>51577000</v>
+      </c>
+      <c r="E54" s="3">
         <v>47626000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>45811000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>45965000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>46890000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>46506000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>44392000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>22631000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2365700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2137500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2061900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2073900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2123700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1868600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1440400</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2767,8 +2895,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2787,296 +2916,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>646000</v>
+      </c>
+      <c r="E57" s="3">
         <v>655000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>678000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1686000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>539000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>929000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>715000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>744000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>127500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>112000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>97000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>94800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>88700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>99000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>92500</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E58" s="3">
         <v>84000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>43000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>45000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>24000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>20000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>375000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>43000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>32900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>24200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>8900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>57100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>12900</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1338000</v>
+      </c>
+      <c r="E59" s="3">
         <v>891000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>760000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>524000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>557000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>675000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>798000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>494000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>70900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>157000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>131300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>161400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>154500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>149500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>92300</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3497000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2642000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2356000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3120000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2086000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2220000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2376000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1668000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>315800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>301900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>252600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>265100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>300300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>199900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>197700</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5103000</v>
+      </c>
+      <c r="E61" s="3">
         <v>5172000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5180000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5205000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5449000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5344000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5161000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5695000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>525600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>468100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>485700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>495800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>490300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>642100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>333100</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2471000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2028000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2202000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2449000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3073000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3534000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3450000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3346000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>101500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>199200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>195900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>201200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>191600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>226500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>187100</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3122,9 +3270,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3170,9 +3321,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3218,57 +3372,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15661000</v>
+      </c>
+      <c r="E66" s="3">
         <v>14370000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>13809000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14676000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14583000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14796000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14565000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13246000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1105400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>969200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>934100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>962100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>982300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1068500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>718000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3287,8 +3447,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3334,9 +3495,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3382,9 +3546,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3430,9 +3597,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3478,57 +3648,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1170000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-5269000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-6713000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-7282000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-6566000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-7949000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-9722000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-13453000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1206700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1177200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1069200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>974500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>881200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>633400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>560200</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3574,9 +3750,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3622,9 +3801,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3670,57 +3852,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>26557000</v>
+      </c>
+      <c r="E76" s="3">
         <v>24290000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>23341000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>22771000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>23857000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>23341000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>21432000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7593000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1260300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1168400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1127800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1111800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1141400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>800100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>722400</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3766,110 +3954,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4993000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2144000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1272000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>432000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2022000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2324000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3969000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1545000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>59400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>135600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>121400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>118400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>270500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>95200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>64700</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3888,56 +4085,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1906000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1914000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2043000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1996000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2099000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2192000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2030000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1453000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>48900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>80200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>78200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>81400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>65100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>57400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>58900</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3983,9 +4184,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4031,9 +4235,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4079,9 +4286,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4127,9 +4337,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4175,57 +4388,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7689000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4491000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3732000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3481000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4378000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5417000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2833000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1765000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>203900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>217600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>217500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>186900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>10100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>136400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>121000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4244,56 +4463,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3821000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3174000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3086000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3049000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2435000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2054000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1701000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1400000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-58700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-47600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-46000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-57400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-57300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-37800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-37100</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4339,9 +4562,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4387,57 +4613,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1236000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2764000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2816000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1711000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1897000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1286000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>50000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1494000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-68000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-179500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-115500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-124200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>157400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-332800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-30600</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4456,56 +4688,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>890000</v>
+      </c>
+      <c r="E96" s="3">
         <v>696000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>700000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1143000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>634000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>547000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>548000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>125000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>29600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-27400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-26200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-24500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-22400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-21700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-18600</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4551,9 +4787,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4599,9 +4838,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4647,151 +4889,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3823000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1795000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1205000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2604000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2388000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2254000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1139000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-925000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-63800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-53300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-59200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-83500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-182800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>219300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-40200</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-6000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-6000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-9000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>6700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1200</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2632000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-74000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-292000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-840000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>92000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1874000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1743000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-663000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>78800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-17500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>37900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-24800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-15500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>23900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>49100</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
